--- a/data/monthly/【2025年11月】月次数値.xlsx
+++ b/data/monthly/【2025年11月】月次数値.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="612" yWindow="600" windowWidth="21792" windowHeight="10812"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="103">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -206,31 +205,152 @@
   </si>
   <si>
     <t>2026-11-25</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>archived</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>千歳烏山ケンズ歯科</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>整体処 たくみ堂</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>金町駅前ジャスミン歯科</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>錦糸町矯正歯科クリニック</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>むぎ歯科</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>はま歯科医院</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>ストレッチ&amp;ボディケア m.o.v.e巣鴨店</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>すがや歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-11-03</t>
+  </si>
+  <si>
+    <t>スカイハイ英語塾</t>
+  </si>
+  <si>
+    <t>きしかわデンタルオフィス</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>PML　広尾店</t>
+  </si>
+  <si>
+    <t>GAJUM photo studio</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -238,36 +358,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -556,14 +676,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:Y18"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y42"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -640,7 +757,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -690,7 +807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -740,7 +857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -790,7 +907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -816,10 +933,10 @@
         <v>2200</v>
       </c>
       <c r="I5">
-        <v>1.505909</v>
+        <v>1.5059089999999999</v>
       </c>
       <c r="J5">
-        <v>56.56470588</v>
+        <v>56.564705879999998</v>
       </c>
       <c r="K5">
         <v>320</v>
@@ -843,28 +960,28 @@
         <v>85</v>
       </c>
       <c r="S5">
-        <v>56.564706</v>
+        <v>56.564706000000001</v>
       </c>
       <c r="T5">
-        <v>2.56565</v>
+        <v>2.5656500000000002</v>
       </c>
       <c r="U5">
         <v>93</v>
       </c>
       <c r="V5">
-        <v>2.807123</v>
+        <v>2.8071229999999998</v>
       </c>
       <c r="W5">
-        <v>51.698925</v>
+        <v>51.698925000000003</v>
       </c>
       <c r="X5">
         <v>54</v>
       </c>
       <c r="Y5">
-        <v>89.037037</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+        <v>89.037036999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -890,10 +1007,10 @@
         <v>1808</v>
       </c>
       <c r="I6">
-        <v>1.544248</v>
+        <v>1.5442480000000001</v>
       </c>
       <c r="J6">
-        <v>49.46391753</v>
+        <v>49.463917530000003</v>
       </c>
       <c r="K6">
         <v>160</v>
@@ -911,7 +1028,7 @@
         <v>2792</v>
       </c>
       <c r="P6">
-        <v>1718.481375</v>
+        <v>1718.4813750000001</v>
       </c>
       <c r="Q6">
         <v>97</v>
@@ -920,7 +1037,7 @@
         <v>49.463918</v>
       </c>
       <c r="T6">
-        <v>3.474212</v>
+        <v>3.4742120000000001</v>
       </c>
       <c r="U6">
         <v>105</v>
@@ -929,16 +1046,16 @@
         <v>3.760745</v>
       </c>
       <c r="W6">
-        <v>45.695238</v>
+        <v>45.695238000000003</v>
       </c>
       <c r="X6">
         <v>84</v>
       </c>
       <c r="Y6">
-        <v>57.119048</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
+        <v>57.119047999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -967,7 +1084,7 @@
         <v>1.377515</v>
       </c>
       <c r="J7">
-        <v>48.57575758</v>
+        <v>48.575757580000001</v>
       </c>
       <c r="K7">
         <v>160</v>
@@ -985,7 +1102,7 @@
         <v>3149</v>
       </c>
       <c r="P7">
-        <v>1527.151477</v>
+        <v>1527.1514770000001</v>
       </c>
       <c r="Q7">
         <v>99</v>
@@ -994,13 +1111,13 @@
         <v>48.575758</v>
       </c>
       <c r="T7">
-        <v>3.143855</v>
+        <v>3.1438549999999998</v>
       </c>
       <c r="U7">
         <v>105</v>
       </c>
       <c r="V7">
-        <v>3.334392</v>
+        <v>3.3343919999999998</v>
       </c>
       <c r="W7">
         <v>45.8</v>
@@ -1009,10 +1126,10 @@
         <v>80</v>
       </c>
       <c r="Y7">
-        <v>60.1125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
+        <v>60.112499999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1041,7 +1158,7 @@
         <v>1.454577</v>
       </c>
       <c r="J8">
-        <v>60.1125</v>
+        <v>60.112499999999997</v>
       </c>
       <c r="K8">
         <v>160</v>
@@ -1059,13 +1176,13 @@
         <v>4131</v>
       </c>
       <c r="P8">
-        <v>1164.124909</v>
+        <v>1164.1249089999999</v>
       </c>
       <c r="Q8">
         <v>80</v>
       </c>
       <c r="S8">
-        <v>60.1125</v>
+        <v>60.112499999999997</v>
       </c>
       <c r="T8">
         <v>1.936577</v>
@@ -1074,10 +1191,10 @@
         <v>95</v>
       </c>
       <c r="V8">
-        <v>2.299685</v>
+        <v>2.2996850000000002</v>
       </c>
       <c r="W8">
-        <v>50.621053</v>
+        <v>50.621053000000003</v>
       </c>
       <c r="X8">
         <v>56</v>
@@ -1086,7 +1203,7 @@
         <v>85.875</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1112,10 +1229,10 @@
         <v>2514</v>
       </c>
       <c r="I9">
-        <v>1.796738</v>
+        <v>1.7967379999999999</v>
       </c>
       <c r="J9">
-        <v>62.50649351</v>
+        <v>62.506493509999999</v>
       </c>
       <c r="K9">
         <v>160</v>
@@ -1139,7 +1256,7 @@
         <v>77</v>
       </c>
       <c r="S9">
-        <v>62.506494</v>
+        <v>62.506494000000004</v>
       </c>
       <c r="T9">
         <v>1.704671</v>
@@ -1148,7 +1265,7 @@
         <v>83</v>
       </c>
       <c r="V9">
-        <v>1.837503</v>
+        <v>1.8375030000000001</v>
       </c>
       <c r="W9">
         <v>57.987952</v>
@@ -1160,7 +1277,7 @@
         <v>75.203125</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1189,7 +1306,7 @@
         <v>1.267123</v>
       </c>
       <c r="J10">
-        <v>43.63636364</v>
+        <v>43.636363639999999</v>
       </c>
       <c r="K10">
         <v>160</v>
@@ -1207,7 +1324,7 @@
         <v>2405</v>
       </c>
       <c r="P10">
-        <v>1995.841996</v>
+        <v>1995.8419960000001</v>
       </c>
       <c r="Q10">
         <v>110</v>
@@ -1216,25 +1333,25 @@
         <v>43.636364</v>
       </c>
       <c r="T10">
-        <v>4.573805</v>
+        <v>4.5738050000000001</v>
       </c>
       <c r="U10">
         <v>118</v>
       </c>
       <c r="V10">
-        <v>4.906445</v>
+        <v>4.9064449999999997</v>
       </c>
       <c r="W10">
-        <v>40.677966</v>
+        <v>40.677965999999998</v>
       </c>
       <c r="X10">
         <v>56</v>
       </c>
       <c r="Y10">
-        <v>85.714286</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+        <v>85.714286000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1263,7 +1380,7 @@
         <v>1.474682</v>
       </c>
       <c r="J11">
-        <v>38.1496063</v>
+        <v>38.149606300000002</v>
       </c>
       <c r="K11">
         <v>160</v>
@@ -1281,25 +1398,25 @@
         <v>4980</v>
       </c>
       <c r="P11">
-        <v>972.891566</v>
+        <v>972.89156600000001</v>
       </c>
       <c r="Q11">
         <v>127</v>
       </c>
       <c r="S11">
-        <v>38.149606</v>
+        <v>38.149605999999999</v>
       </c>
       <c r="T11">
-        <v>2.550201</v>
+        <v>2.5502009999999999</v>
       </c>
       <c r="U11">
         <v>145</v>
       </c>
       <c r="V11">
-        <v>2.911647</v>
+        <v>2.9116469999999999</v>
       </c>
       <c r="W11">
-        <v>33.413793</v>
+        <v>33.413792999999998</v>
       </c>
       <c r="X11">
         <v>100</v>
@@ -1308,7 +1425,7 @@
         <v>48.45</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1334,10 +1451,10 @@
         <v>4380</v>
       </c>
       <c r="I12">
-        <v>1.548858</v>
+        <v>1.5488580000000001</v>
       </c>
       <c r="J12">
-        <v>22.504</v>
+        <v>22.504000000000001</v>
       </c>
       <c r="K12" t="s">
         <v>34</v>
@@ -1355,22 +1472,22 @@
         <v>6784</v>
       </c>
       <c r="P12">
-        <v>829.304245</v>
+        <v>829.30424500000004</v>
       </c>
       <c r="Q12">
         <v>260</v>
       </c>
       <c r="S12">
-        <v>21.638462</v>
+        <v>21.638462000000001</v>
       </c>
       <c r="T12">
-        <v>3.832547</v>
+        <v>3.8325469999999999</v>
       </c>
       <c r="U12">
         <v>352</v>
       </c>
       <c r="V12">
-        <v>5.188679</v>
+        <v>5.1886789999999996</v>
       </c>
       <c r="W12">
         <v>15.982955</v>
@@ -1379,10 +1496,10 @@
         <v>250</v>
       </c>
       <c r="Y12">
-        <v>22.504</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
+        <v>22.504000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1408,10 +1525,10 @@
         <v>1772</v>
       </c>
       <c r="I13">
-        <v>1.623025</v>
+        <v>1.6230249999999999</v>
       </c>
       <c r="J13">
-        <v>51.06756757</v>
+        <v>51.067567570000001</v>
       </c>
       <c r="K13" t="s">
         <v>34</v>
@@ -1429,34 +1546,34 @@
         <v>2876</v>
       </c>
       <c r="P13">
-        <v>1313.977747</v>
+        <v>1313.9777469999999</v>
       </c>
       <c r="Q13">
         <v>84</v>
       </c>
       <c r="S13">
-        <v>44.988095</v>
+        <v>44.988095000000001</v>
       </c>
       <c r="T13">
-        <v>2.920723</v>
+        <v>2.9207230000000002</v>
       </c>
       <c r="U13">
         <v>104</v>
       </c>
       <c r="V13">
-        <v>3.616134</v>
+        <v>3.6161340000000002</v>
       </c>
       <c r="W13">
-        <v>36.336538</v>
+        <v>36.336537999999997</v>
       </c>
       <c r="X13">
         <v>74</v>
       </c>
       <c r="Y13">
-        <v>51.067568</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
+        <v>51.067568000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1485,7 +1602,7 @@
         <v>1.340317</v>
       </c>
       <c r="J14">
-        <v>89.45454545</v>
+        <v>89.454545449999998</v>
       </c>
       <c r="K14" t="s">
         <v>34</v>
@@ -1503,7 +1620,7 @@
         <v>2111</v>
       </c>
       <c r="P14">
-        <v>1398.389389</v>
+        <v>1398.3893889999999</v>
       </c>
       <c r="Q14">
         <v>32</v>
@@ -1512,25 +1629,25 @@
         <v>92.25</v>
       </c>
       <c r="T14">
-        <v>1.515869</v>
+        <v>1.5158689999999999</v>
       </c>
       <c r="U14">
         <v>43</v>
       </c>
       <c r="V14">
-        <v>2.036949</v>
+        <v>2.0369489999999999</v>
       </c>
       <c r="W14">
-        <v>68.651163</v>
+        <v>68.651162999999997</v>
       </c>
       <c r="X14">
         <v>33</v>
       </c>
       <c r="Y14">
-        <v>89.454545</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
+        <v>89.454544999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1556,7 +1673,7 @@
         <v>1184</v>
       </c>
       <c r="I15">
-        <v>1.261824</v>
+        <v>1.2618240000000001</v>
       </c>
       <c r="J15">
         <v>60.125</v>
@@ -1577,25 +1694,25 @@
         <v>1494</v>
       </c>
       <c r="P15">
-        <v>1287.817938</v>
+        <v>1287.8179379999999</v>
       </c>
       <c r="Q15">
         <v>35</v>
       </c>
       <c r="S15">
-        <v>54.971429</v>
+        <v>54.971429000000001</v>
       </c>
       <c r="T15">
-        <v>2.342704</v>
+        <v>2.3427039999999999</v>
       </c>
       <c r="U15">
         <v>43</v>
       </c>
       <c r="V15">
-        <v>2.878179</v>
+        <v>2.8781789999999998</v>
       </c>
       <c r="W15">
-        <v>44.744186</v>
+        <v>44.744185999999999</v>
       </c>
       <c r="X15">
         <v>32</v>
@@ -1604,7 +1721,7 @@
         <v>60.125</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1630,7 +1747,7 @@
         <v>642</v>
       </c>
       <c r="I16">
-        <v>1.038941</v>
+        <v>1.0389409999999999</v>
       </c>
       <c r="J16">
         <v>120.875</v>
@@ -1660,7 +1777,7 @@
         <v>107.444444</v>
       </c>
       <c r="T16">
-        <v>1.349325</v>
+        <v>1.3493250000000001</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -1678,7 +1795,7 @@
         <v>120.875</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1704,10 +1821,10 @@
         <v>746</v>
       </c>
       <c r="I17">
-        <v>1.095174</v>
+        <v>1.0951740000000001</v>
       </c>
       <c r="J17">
-        <v>77.4</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="K17" t="s">
         <v>34</v>
@@ -1725,7 +1842,7 @@
         <v>817</v>
       </c>
       <c r="P17">
-        <v>1421.052632</v>
+        <v>1421.0526319999999</v>
       </c>
       <c r="Q17">
         <v>16</v>
@@ -1734,13 +1851,13 @@
         <v>72.5625</v>
       </c>
       <c r="T17">
-        <v>1.958384</v>
+        <v>1.9583839999999999</v>
       </c>
       <c r="U17">
         <v>20</v>
       </c>
       <c r="V17">
-        <v>2.44798</v>
+        <v>2.4479799999999998</v>
       </c>
       <c r="W17">
         <v>58.05</v>
@@ -1749,10 +1866,10 @@
         <v>15</v>
       </c>
       <c r="Y17">
-        <v>77.4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+        <v>77.400000000000006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1778,10 +1895,10 @@
         <v>529</v>
       </c>
       <c r="I18">
-        <v>1.124764</v>
+        <v>1.1247640000000001</v>
       </c>
       <c r="J18">
-        <v>115.22222222</v>
+        <v>115.22222222000001</v>
       </c>
       <c r="K18" t="s">
         <v>34</v>
@@ -1826,18 +1943,1684 @@
         <v>115.222222</v>
       </c>
     </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19">
+        <v>157</v>
+      </c>
+      <c r="G19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19">
+        <v>2418</v>
+      </c>
+      <c r="I19">
+        <v>1.2853600000000001</v>
+      </c>
+      <c r="J19">
+        <v>39.019108279999998</v>
+      </c>
+      <c r="K19" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>6126</v>
+      </c>
+      <c r="N19" t="s">
+        <v>101</v>
+      </c>
+      <c r="O19">
+        <v>3108</v>
+      </c>
+      <c r="P19">
+        <v>1971.042471</v>
+      </c>
+      <c r="Q19">
+        <v>157</v>
+      </c>
+      <c r="S19">
+        <v>39.019108000000003</v>
+      </c>
+      <c r="T19">
+        <v>5.0514799999999997</v>
+      </c>
+      <c r="U19">
+        <v>160</v>
+      </c>
+      <c r="V19">
+        <v>5.1480050000000004</v>
+      </c>
+      <c r="W19">
+        <v>38.287500000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20">
+        <v>95</v>
+      </c>
+      <c r="G20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20">
+        <v>5184</v>
+      </c>
+      <c r="I20">
+        <v>1.3780859999999999</v>
+      </c>
+      <c r="J20">
+        <v>62.189473679999999</v>
+      </c>
+      <c r="K20" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>5908</v>
+      </c>
+      <c r="N20" t="s">
+        <v>91</v>
+      </c>
+      <c r="O20">
+        <v>7144</v>
+      </c>
+      <c r="P20">
+        <v>826.98768199999995</v>
+      </c>
+      <c r="Q20">
+        <v>95</v>
+      </c>
+      <c r="S20">
+        <v>62.189473999999997</v>
+      </c>
+      <c r="T20">
+        <v>1.3297870000000001</v>
+      </c>
+      <c r="U20">
+        <v>104</v>
+      </c>
+      <c r="V20">
+        <v>1.455767</v>
+      </c>
+      <c r="W20">
+        <v>56.807692000000003</v>
+      </c>
+      <c r="X20">
+        <v>71</v>
+      </c>
+      <c r="Y20">
+        <v>83.211268000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21">
+        <v>121</v>
+      </c>
+      <c r="G21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21">
+        <v>4800</v>
+      </c>
+      <c r="I21">
+        <v>1.3725000000000001</v>
+      </c>
+      <c r="J21">
+        <v>56.099173550000003</v>
+      </c>
+      <c r="K21" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>6788</v>
+      </c>
+      <c r="N21" t="s">
+        <v>98</v>
+      </c>
+      <c r="O21">
+        <v>6588</v>
+      </c>
+      <c r="P21">
+        <v>1030.3582269999999</v>
+      </c>
+      <c r="Q21">
+        <v>162</v>
+      </c>
+      <c r="S21">
+        <v>41.901235</v>
+      </c>
+      <c r="T21">
+        <v>2.4590160000000001</v>
+      </c>
+      <c r="U21">
+        <v>164</v>
+      </c>
+      <c r="V21">
+        <v>2.4893749999999999</v>
+      </c>
+      <c r="W21">
+        <v>41.390244000000003</v>
+      </c>
+      <c r="X21">
+        <v>121</v>
+      </c>
+      <c r="Y21">
+        <v>56.099173999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22">
+        <v>83</v>
+      </c>
+      <c r="G22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22">
+        <v>2859</v>
+      </c>
+      <c r="I22">
+        <v>1.1346620000000001</v>
+      </c>
+      <c r="J22">
+        <v>72.204819279999995</v>
+      </c>
+      <c r="K22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>5993</v>
+      </c>
+      <c r="N22" t="s">
+        <v>62</v>
+      </c>
+      <c r="O22">
+        <v>3244</v>
+      </c>
+      <c r="P22">
+        <v>1847.4106039999999</v>
+      </c>
+      <c r="Q22">
+        <v>83</v>
+      </c>
+      <c r="S22">
+        <v>72.204819000000001</v>
+      </c>
+      <c r="T22">
+        <v>2.55857</v>
+      </c>
+      <c r="U22">
+        <v>88</v>
+      </c>
+      <c r="V22">
+        <v>2.7126999999999999</v>
+      </c>
+      <c r="W22">
+        <v>68.102272999999997</v>
+      </c>
+      <c r="X22">
+        <v>35</v>
+      </c>
+      <c r="Y22">
+        <v>171.22857099999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23">
+        <v>67</v>
+      </c>
+      <c r="G23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23">
+        <v>3439</v>
+      </c>
+      <c r="I23">
+        <v>1.5891249999999999</v>
+      </c>
+      <c r="J23">
+        <v>78.40298507</v>
+      </c>
+      <c r="K23" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>5253</v>
+      </c>
+      <c r="N23" t="s">
+        <v>95</v>
+      </c>
+      <c r="O23">
+        <v>5465</v>
+      </c>
+      <c r="P23">
+        <v>961.20768499999997</v>
+      </c>
+      <c r="Q23">
+        <v>130</v>
+      </c>
+      <c r="S23">
+        <v>40.407691999999997</v>
+      </c>
+      <c r="T23">
+        <v>2.3787739999999999</v>
+      </c>
+      <c r="U23">
+        <v>134</v>
+      </c>
+      <c r="V23">
+        <v>2.4519669999999998</v>
+      </c>
+      <c r="W23">
+        <v>39.201492999999999</v>
+      </c>
+      <c r="X23">
+        <v>67</v>
+      </c>
+      <c r="Y23">
+        <v>78.402985000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24">
+        <v>131</v>
+      </c>
+      <c r="G24" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24">
+        <v>3732</v>
+      </c>
+      <c r="I24">
+        <v>1.6256699999999999</v>
+      </c>
+      <c r="J24">
+        <v>44.030534350000003</v>
+      </c>
+      <c r="K24" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>5768</v>
+      </c>
+      <c r="N24" t="s">
+        <v>93</v>
+      </c>
+      <c r="O24">
+        <v>6067</v>
+      </c>
+      <c r="P24">
+        <v>950.716994</v>
+      </c>
+      <c r="Q24">
+        <v>131</v>
+      </c>
+      <c r="S24">
+        <v>44.030534000000003</v>
+      </c>
+      <c r="T24">
+        <v>2.1592220000000002</v>
+      </c>
+      <c r="U24">
+        <v>163</v>
+      </c>
+      <c r="V24">
+        <v>2.6866660000000002</v>
+      </c>
+      <c r="W24">
+        <v>35.386502999999998</v>
+      </c>
+      <c r="X24">
+        <v>106</v>
+      </c>
+      <c r="Y24">
+        <v>54.415094000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25">
+        <v>156</v>
+      </c>
+      <c r="G25" t="s">
+        <v>39</v>
+      </c>
+      <c r="H25">
+        <v>3240</v>
+      </c>
+      <c r="I25">
+        <v>1.217284</v>
+      </c>
+      <c r="J25">
+        <v>39.089743589999998</v>
+      </c>
+      <c r="K25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>6098</v>
+      </c>
+      <c r="N25" t="s">
+        <v>91</v>
+      </c>
+      <c r="O25">
+        <v>3944</v>
+      </c>
+      <c r="P25">
+        <v>1546.146045</v>
+      </c>
+      <c r="Q25">
+        <v>156</v>
+      </c>
+      <c r="S25">
+        <v>39.089744000000003</v>
+      </c>
+      <c r="T25">
+        <v>3.9553750000000001</v>
+      </c>
+      <c r="U25">
+        <v>166</v>
+      </c>
+      <c r="V25">
+        <v>4.2089249999999998</v>
+      </c>
+      <c r="W25">
+        <v>36.734940000000002</v>
+      </c>
+      <c r="X25">
+        <v>118</v>
+      </c>
+      <c r="Y25">
+        <v>51.677965999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26">
+        <v>187</v>
+      </c>
+      <c r="G26" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26">
+        <v>2929</v>
+      </c>
+      <c r="I26">
+        <v>1.3656539999999999</v>
+      </c>
+      <c r="J26">
+        <v>31.737967909999998</v>
+      </c>
+      <c r="K26" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>5935</v>
+      </c>
+      <c r="N26" t="s">
+        <v>77</v>
+      </c>
+      <c r="O26">
+        <v>4000</v>
+      </c>
+      <c r="P26">
+        <v>1483.75</v>
+      </c>
+      <c r="Q26">
+        <v>187</v>
+      </c>
+      <c r="S26">
+        <v>31.737967999999999</v>
+      </c>
+      <c r="T26">
+        <v>4.6749999999999998</v>
+      </c>
+      <c r="U26">
+        <v>189</v>
+      </c>
+      <c r="V26">
+        <v>4.7249999999999996</v>
+      </c>
+      <c r="W26">
+        <v>31.402115999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27">
+        <v>103</v>
+      </c>
+      <c r="G27" t="s">
+        <v>39</v>
+      </c>
+      <c r="H27">
+        <v>5162</v>
+      </c>
+      <c r="I27">
+        <v>1.495932</v>
+      </c>
+      <c r="J27">
+        <v>61.495145630000003</v>
+      </c>
+      <c r="K27" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>6334</v>
+      </c>
+      <c r="N27" t="s">
+        <v>88</v>
+      </c>
+      <c r="O27">
+        <v>7722</v>
+      </c>
+      <c r="P27">
+        <v>820.25382000000002</v>
+      </c>
+      <c r="Q27">
+        <v>103</v>
+      </c>
+      <c r="S27">
+        <v>61.495145999999998</v>
+      </c>
+      <c r="T27">
+        <v>1.3338509999999999</v>
+      </c>
+      <c r="U27">
+        <v>106</v>
+      </c>
+      <c r="V27">
+        <v>1.3727009999999999</v>
+      </c>
+      <c r="W27">
+        <v>59.754716999999999</v>
+      </c>
+      <c r="X27">
+        <v>49</v>
+      </c>
+      <c r="Y27">
+        <v>129.26530600000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28">
+        <v>222</v>
+      </c>
+      <c r="G28" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28">
+        <v>3690</v>
+      </c>
+      <c r="I28">
+        <v>1.1962060000000001</v>
+      </c>
+      <c r="J28">
+        <v>25.527027029999999</v>
+      </c>
+      <c r="K28" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>5667</v>
+      </c>
+      <c r="N28" t="s">
+        <v>67</v>
+      </c>
+      <c r="O28">
+        <v>4414</v>
+      </c>
+      <c r="P28">
+        <v>1283.869506</v>
+      </c>
+      <c r="Q28">
+        <v>222</v>
+      </c>
+      <c r="S28">
+        <v>25.527027</v>
+      </c>
+      <c r="T28">
+        <v>5.029452</v>
+      </c>
+      <c r="U28">
+        <v>236</v>
+      </c>
+      <c r="V28">
+        <v>5.3466240000000003</v>
+      </c>
+      <c r="W28">
+        <v>24.012712000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29">
+        <v>170</v>
+      </c>
+      <c r="G29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H29">
+        <v>3274</v>
+      </c>
+      <c r="I29">
+        <v>1.4523520000000001</v>
+      </c>
+      <c r="J29">
+        <v>35.852941180000002</v>
+      </c>
+      <c r="K29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>6095</v>
+      </c>
+      <c r="N29" t="s">
+        <v>85</v>
+      </c>
+      <c r="O29">
+        <v>4755</v>
+      </c>
+      <c r="P29">
+        <v>1281.8086229999999</v>
+      </c>
+      <c r="Q29">
+        <v>170</v>
+      </c>
+      <c r="S29">
+        <v>35.852941000000001</v>
+      </c>
+      <c r="T29">
+        <v>3.5751840000000001</v>
+      </c>
+      <c r="U29">
+        <v>182</v>
+      </c>
+      <c r="V29">
+        <v>3.82755</v>
+      </c>
+      <c r="W29">
+        <v>33.489010999999998</v>
+      </c>
+      <c r="X29">
+        <v>146</v>
+      </c>
+      <c r="Y29">
+        <v>41.746575</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30">
+        <v>123</v>
+      </c>
+      <c r="G30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H30">
+        <v>3319</v>
+      </c>
+      <c r="I30">
+        <v>1.5335939999999999</v>
+      </c>
+      <c r="J30">
+        <v>46.414634149999998</v>
+      </c>
+      <c r="K30" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>5709</v>
+      </c>
+      <c r="N30" t="s">
+        <v>77</v>
+      </c>
+      <c r="O30">
+        <v>5090</v>
+      </c>
+      <c r="P30">
+        <v>1121.6110020000001</v>
+      </c>
+      <c r="Q30">
+        <v>123</v>
+      </c>
+      <c r="S30">
+        <v>46.414634</v>
+      </c>
+      <c r="T30">
+        <v>2.4165030000000001</v>
+      </c>
+      <c r="U30">
+        <v>131</v>
+      </c>
+      <c r="V30">
+        <v>2.573674</v>
+      </c>
+      <c r="W30">
+        <v>43.580153000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31">
+        <v>224</v>
+      </c>
+      <c r="G31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H31">
+        <v>4514</v>
+      </c>
+      <c r="I31">
+        <v>1.3203370000000001</v>
+      </c>
+      <c r="J31">
+        <v>25.941964290000001</v>
+      </c>
+      <c r="K31" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>5811</v>
+      </c>
+      <c r="N31" t="s">
+        <v>82</v>
+      </c>
+      <c r="O31">
+        <v>5960</v>
+      </c>
+      <c r="P31">
+        <v>975</v>
+      </c>
+      <c r="Q31">
+        <v>224</v>
+      </c>
+      <c r="S31">
+        <v>25.941963999999999</v>
+      </c>
+      <c r="T31">
+        <v>3.7583890000000002</v>
+      </c>
+      <c r="U31">
+        <v>279</v>
+      </c>
+      <c r="V31">
+        <v>4.6812079999999998</v>
+      </c>
+      <c r="W31">
+        <v>20.827957000000001</v>
+      </c>
+      <c r="X31">
+        <v>189</v>
+      </c>
+      <c r="Y31">
+        <v>30.746032</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>34</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>80</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" t="s">
+        <v>68</v>
+      </c>
+      <c r="E33" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33">
+        <v>51</v>
+      </c>
+      <c r="G33" t="s">
+        <v>39</v>
+      </c>
+      <c r="H33">
+        <v>1935</v>
+      </c>
+      <c r="I33">
+        <v>2.843928</v>
+      </c>
+      <c r="J33">
+        <v>109.94117647</v>
+      </c>
+      <c r="K33" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>5607</v>
+      </c>
+      <c r="N33" t="s">
+        <v>35</v>
+      </c>
+      <c r="O33">
+        <v>5503</v>
+      </c>
+      <c r="P33">
+        <v>1018.898782</v>
+      </c>
+      <c r="Q33">
+        <v>51</v>
+      </c>
+      <c r="S33">
+        <v>109.941176</v>
+      </c>
+      <c r="T33">
+        <v>0.92676700000000001</v>
+      </c>
+      <c r="U33">
+        <v>53</v>
+      </c>
+      <c r="V33">
+        <v>0.96311100000000005</v>
+      </c>
+      <c r="W33">
+        <v>105.79245299999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34">
+        <v>90</v>
+      </c>
+      <c r="G34" t="s">
+        <v>39</v>
+      </c>
+      <c r="H34">
+        <v>3299</v>
+      </c>
+      <c r="I34">
+        <v>1.346166</v>
+      </c>
+      <c r="J34">
+        <v>65.555555560000002</v>
+      </c>
+      <c r="K34" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>5900</v>
+      </c>
+      <c r="N34" t="s">
+        <v>77</v>
+      </c>
+      <c r="O34">
+        <v>4441</v>
+      </c>
+      <c r="P34">
+        <v>1328.52961</v>
+      </c>
+      <c r="Q34">
+        <v>90</v>
+      </c>
+      <c r="S34">
+        <v>65.555555999999996</v>
+      </c>
+      <c r="T34">
+        <v>2.0265710000000001</v>
+      </c>
+      <c r="U34">
+        <v>96</v>
+      </c>
+      <c r="V34">
+        <v>2.1616749999999998</v>
+      </c>
+      <c r="W34">
+        <v>61.458333000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35">
+        <v>123</v>
+      </c>
+      <c r="G35" t="s">
+        <v>39</v>
+      </c>
+      <c r="H35">
+        <v>2025</v>
+      </c>
+      <c r="I35">
+        <v>1.304198</v>
+      </c>
+      <c r="J35">
+        <v>52.68292683</v>
+      </c>
+      <c r="K35" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>6480</v>
+      </c>
+      <c r="N35" t="s">
+        <v>75</v>
+      </c>
+      <c r="O35">
+        <v>2641</v>
+      </c>
+      <c r="P35">
+        <v>2453.616055</v>
+      </c>
+      <c r="Q35">
+        <v>123</v>
+      </c>
+      <c r="S35">
+        <v>52.682926999999999</v>
+      </c>
+      <c r="T35">
+        <v>4.6573270000000004</v>
+      </c>
+      <c r="U35">
+        <v>134</v>
+      </c>
+      <c r="V35">
+        <v>5.073836</v>
+      </c>
+      <c r="W35">
+        <v>48.358209000000002</v>
+      </c>
+      <c r="X35">
+        <v>5</v>
+      </c>
+      <c r="Y35">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36">
+        <v>102</v>
+      </c>
+      <c r="G36" t="s">
+        <v>39</v>
+      </c>
+      <c r="H36">
+        <v>4496</v>
+      </c>
+      <c r="I36">
+        <v>1.421708</v>
+      </c>
+      <c r="J36">
+        <v>58.764705880000001</v>
+      </c>
+      <c r="K36" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>5994</v>
+      </c>
+      <c r="N36" t="s">
+        <v>73</v>
+      </c>
+      <c r="O36">
+        <v>6392</v>
+      </c>
+      <c r="P36">
+        <v>937.73466800000006</v>
+      </c>
+      <c r="Q36">
+        <v>102</v>
+      </c>
+      <c r="S36">
+        <v>58.764705999999997</v>
+      </c>
+      <c r="T36">
+        <v>1.595745</v>
+      </c>
+      <c r="U36">
+        <v>106</v>
+      </c>
+      <c r="V36">
+        <v>1.658323</v>
+      </c>
+      <c r="W36">
+        <v>56.547170000000001</v>
+      </c>
+      <c r="X36">
+        <v>72</v>
+      </c>
+      <c r="Y36">
+        <v>83.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37">
+        <v>72</v>
+      </c>
+      <c r="G37" t="s">
+        <v>39</v>
+      </c>
+      <c r="H37">
+        <v>3418</v>
+      </c>
+      <c r="I37">
+        <v>1.2776479999999999</v>
+      </c>
+      <c r="J37">
+        <v>80.652777779999994</v>
+      </c>
+      <c r="K37" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>5807</v>
+      </c>
+      <c r="N37" t="s">
+        <v>71</v>
+      </c>
+      <c r="O37">
+        <v>4367</v>
+      </c>
+      <c r="P37">
+        <v>1329.745821</v>
+      </c>
+      <c r="Q37">
+        <v>72</v>
+      </c>
+      <c r="S37">
+        <v>80.652777999999998</v>
+      </c>
+      <c r="T37">
+        <v>1.6487289999999999</v>
+      </c>
+      <c r="U37">
+        <v>78</v>
+      </c>
+      <c r="V37">
+        <v>1.7861229999999999</v>
+      </c>
+      <c r="W37">
+        <v>74.448718</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38">
+        <v>93</v>
+      </c>
+      <c r="G38" t="s">
+        <v>39</v>
+      </c>
+      <c r="H38">
+        <v>3815</v>
+      </c>
+      <c r="I38">
+        <v>1.245085</v>
+      </c>
+      <c r="J38">
+        <v>63.623655909999997</v>
+      </c>
+      <c r="K38" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>5917</v>
+      </c>
+      <c r="N38" t="s">
+        <v>70</v>
+      </c>
+      <c r="O38">
+        <v>4750</v>
+      </c>
+      <c r="P38">
+        <v>1245.684211</v>
+      </c>
+      <c r="Q38">
+        <v>93</v>
+      </c>
+      <c r="S38">
+        <v>63.623655999999997</v>
+      </c>
+      <c r="T38">
+        <v>1.9578949999999999</v>
+      </c>
+      <c r="U38">
+        <v>97</v>
+      </c>
+      <c r="V38">
+        <v>2.0421049999999998</v>
+      </c>
+      <c r="W38">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39">
+        <v>108</v>
+      </c>
+      <c r="G39" t="s">
+        <v>39</v>
+      </c>
+      <c r="H39">
+        <v>3085</v>
+      </c>
+      <c r="I39">
+        <v>1.2411669999999999</v>
+      </c>
+      <c r="J39">
+        <v>53.194444439999998</v>
+      </c>
+      <c r="K39" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>5745</v>
+      </c>
+      <c r="N39" t="s">
+        <v>67</v>
+      </c>
+      <c r="O39">
+        <v>3829</v>
+      </c>
+      <c r="P39">
+        <v>1500.3917469999999</v>
+      </c>
+      <c r="Q39">
+        <v>108</v>
+      </c>
+      <c r="S39">
+        <v>53.194443999999997</v>
+      </c>
+      <c r="T39">
+        <v>2.8205800000000001</v>
+      </c>
+      <c r="U39">
+        <v>109</v>
+      </c>
+      <c r="V39">
+        <v>2.8466960000000001</v>
+      </c>
+      <c r="W39">
+        <v>52.706422000000003</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40" t="s">
+        <v>65</v>
+      </c>
+      <c r="H40">
+        <v>19</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="K40" t="s">
+        <v>34</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>24</v>
+      </c>
+      <c r="N40" t="s">
+        <v>64</v>
+      </c>
+      <c r="O40">
+        <v>19</v>
+      </c>
+      <c r="P40">
+        <v>1263.1578950000001</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" t="s">
+        <v>66</v>
+      </c>
+      <c r="E41" t="s">
+        <v>65</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H41">
+        <v>24</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>8</v>
+      </c>
+      <c r="K41" t="s">
+        <v>34</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>16</v>
+      </c>
+      <c r="N41" t="s">
+        <v>64</v>
+      </c>
+      <c r="O41">
+        <v>24</v>
+      </c>
+      <c r="P41">
+        <v>666.66666699999996</v>
+      </c>
+      <c r="Q41">
+        <v>2</v>
+      </c>
+      <c r="S41">
+        <v>8</v>
+      </c>
+      <c r="T41">
+        <v>8.3333329999999997</v>
+      </c>
+      <c r="U41">
+        <v>1</v>
+      </c>
+      <c r="V41">
+        <v>4.1666670000000003</v>
+      </c>
+      <c r="W41">
+        <v>16</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+      <c r="Y41">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42">
+        <v>138</v>
+      </c>
+      <c r="G42" t="s">
+        <v>39</v>
+      </c>
+      <c r="H42">
+        <v>2917</v>
+      </c>
+      <c r="I42">
+        <v>1.2255739999999999</v>
+      </c>
+      <c r="J42">
+        <v>45.260869569999997</v>
+      </c>
+      <c r="K42" t="s">
+        <v>34</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>6246</v>
+      </c>
+      <c r="N42" t="s">
+        <v>62</v>
+      </c>
+      <c r="O42">
+        <v>3575</v>
+      </c>
+      <c r="P42">
+        <v>1747.132867</v>
+      </c>
+      <c r="Q42">
+        <v>138</v>
+      </c>
+      <c r="S42">
+        <v>45.260869999999997</v>
+      </c>
+      <c r="T42">
+        <v>3.8601399999999999</v>
+      </c>
+      <c r="U42">
+        <v>147</v>
+      </c>
+      <c r="V42">
+        <v>4.1118880000000004</v>
+      </c>
+      <c r="W42">
+        <v>42.489795999999998</v>
+      </c>
+      <c r="X42">
+        <v>128</v>
+      </c>
+      <c r="Y42">
+        <v>48.796875</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>